--- a/data/trans_camb/P38A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 9,61</t>
+          <t>-4,55; 9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,32</t>
+          <t>-12,02; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,32</t>
+          <t>-3,12; 9,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 9,48</t>
+          <t>-6,98; 9,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,17</t>
+          <t>-2,07; 7,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 4,82</t>
+          <t>-7,88; 4,49</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 18,62</t>
+          <t>-7,75; 17,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 13,62</t>
+          <t>-21,52; 15,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 15,07</t>
+          <t>-4,61; 15,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 14,89</t>
+          <t>-10,41; 15,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 14,53</t>
+          <t>-3,33; 12,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 8,09</t>
+          <t>-13,04; 7,7</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -1,48</t>
+          <t>-11,17; -1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -2,79</t>
+          <t>-15,54; -3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,68</t>
+          <t>-4,18; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,2; -5,31</t>
+          <t>-45,82; -5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; -0,31</t>
+          <t>-6,25; -0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,47; -5,99</t>
+          <t>-34,15; -6,27</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -1,85</t>
+          <t>-13,5; -2,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; -3,5</t>
+          <t>-18,44; -3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,3</t>
+          <t>-4,65; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -6,14</t>
+          <t>-52,42; -6,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,37</t>
+          <t>-7,23; -0,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,23; -7,12</t>
+          <t>-40,03; -7,53</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -0,1</t>
+          <t>-8,2; 0,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -0,02</t>
+          <t>-8,16; -0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; -1,46</t>
+          <t>-7,74; -1,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -3,51</t>
+          <t>-9,33; -3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -1,84</t>
+          <t>-6,91; -1,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -2,69</t>
+          <t>-7,84; -2,68</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -0,15</t>
+          <t>-9,33; 0,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -0,0</t>
+          <t>-9,3; -0,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,1; -1,59</t>
+          <t>-8,26; -1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -3,79</t>
+          <t>-9,88; -3,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -2,06</t>
+          <t>-7,58; -1,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -3,02</t>
+          <t>-8,67; -3,03</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -0,63</t>
+          <t>-7,51; -0,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-63,4; -2,35</t>
+          <t>-65,69; -1,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,49</t>
+          <t>-1,8; 4,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,3</t>
+          <t>-0,34; 5,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,0</t>
+          <t>-3,68; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 0,14</t>
+          <t>-42,73; 0,33</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -0,71</t>
+          <t>-7,96; -0,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,63; -2,54</t>
+          <t>-70,64; -2,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,04</t>
+          <t>-1,91; 5,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,96</t>
+          <t>-0,37; 6,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,1</t>
+          <t>-3,96; 1,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 0,14</t>
+          <t>-45,58; 0,37</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,75</t>
+          <t>-4,86; 1,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,09</t>
+          <t>-5,4; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,01</t>
+          <t>-3,24; 2,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,24</t>
+          <t>-2,64; 2,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,14</t>
+          <t>-3,29; 1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,61</t>
+          <t>-3,21; 0,8</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 1,85</t>
+          <t>-5,0; 1,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,12</t>
+          <t>-5,56; 1,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,15</t>
+          <t>-3,36; 2,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,4</t>
+          <t>-2,74; 2,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,21</t>
+          <t>-3,42; 1,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,65</t>
+          <t>-3,34; 0,85</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,21</t>
+          <t>-2,41; 2,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,31</t>
+          <t>-3,17; 1,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,14</t>
+          <t>0,21; 5,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,62</t>
+          <t>0,56; 5,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,97</t>
+          <t>-0,44; 3,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,21</t>
+          <t>-0,67; 3,19</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,29</t>
+          <t>-2,43; 2,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,37</t>
+          <t>-3,22; 1,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,52</t>
+          <t>0,24; 5,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,02</t>
+          <t>0,58; 6,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,12</t>
+          <t>-0,45; 3,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,36</t>
+          <t>-0,68; 3,36</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,78</t>
+          <t>-1,65; 3,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,63</t>
+          <t>-1,14; 3,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,44</t>
+          <t>-2,4; 1,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,54</t>
+          <t>-4,12; -0,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,52</t>
+          <t>-1,35; 1,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,6</t>
+          <t>-2,34; 0,48</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,0</t>
+          <t>-1,66; 4,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,92</t>
+          <t>-1,15; 3,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,47</t>
+          <t>-2,42; 1,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,58</t>
+          <t>-4,15; -0,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,56</t>
+          <t>-1,35; 1,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,61</t>
+          <t>-2,37; 0,49</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,11</t>
+          <t>-3,55; 0,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -0,99</t>
+          <t>-25,32; -1,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,6</t>
+          <t>-1,36; 1,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,06</t>
+          <t>-7,16; 1,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,37</t>
+          <t>-1,83; 0,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -0,63</t>
+          <t>-14,12; -0,77</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,14</t>
+          <t>-4,12; 0,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,58; -1,16</t>
+          <t>-29,6; -1,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,81</t>
+          <t>-1,5; 1,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,18</t>
+          <t>-7,99; 1,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,43</t>
+          <t>-2,08; 0,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -0,73</t>
+          <t>-16,3; -0,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-6,34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-3,85</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 9,09</t>
+          <t>-5,25; 8,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 8,0</t>
+          <t>-15,45; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 9,71</t>
+          <t>-3,44; 9,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 9,52</t>
+          <t>-9,52; 7,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 7,2</t>
+          <t>-2,03; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 4,49</t>
+          <t>-10,08; 2,18</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-11,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>-1,08%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,95%</t>
+          <t>-6,46%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 17,92</t>
+          <t>-8,67; 17,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 15,41</t>
+          <t>-26,36; 5,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 15,94</t>
+          <t>-4,94; 15,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 15,48</t>
+          <t>-14,28; 11,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 12,64</t>
+          <t>-3,29; 12,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 7,7</t>
+          <t>-16,34; 4,1</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-8,93</t>
+          <t>-9,99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,1</t>
+          <t>-8,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,5</t>
+          <t>-9,15</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -1,53</t>
+          <t>-10,68; -0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,54; -3,02</t>
+          <t>-16,54; -3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,78</t>
+          <t>-4,46; 3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,82; -5,83</t>
+          <t>-13,45; -4,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,36</t>
+          <t>-6,26; -0,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,15; -6,27</t>
+          <t>-13,26; -5,59</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-12,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-20,71%</t>
+          <t>-10,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,02%</t>
+          <t>-10,86%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -2,09</t>
+          <t>-12,82; -0,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -3,75</t>
+          <t>-20,31; -5,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 4,43</t>
+          <t>-4,97; 3,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; -6,67</t>
+          <t>-15,24; -4,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,42</t>
+          <t>-7,28; -0,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,03; -7,53</t>
+          <t>-15,64; -6,79</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>-6,84</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-6,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,27</t>
+          <t>-6,88</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 0,32</t>
+          <t>-8,12; -0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -0,0</t>
+          <t>-11,33; -2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -1,61</t>
+          <t>-7,7; -1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -3,48</t>
+          <t>-9,76; -3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -1,78</t>
+          <t>-6,97; -2,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; -2,68</t>
+          <t>-9,59; -4,27</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4,71%</t>
+          <t>-7,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,75%</t>
+          <t>-7,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-5,84%</t>
+          <t>-7,64%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,38</t>
+          <t>-9,21; -0,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,01</t>
+          <t>-12,97; -2,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -1,76</t>
+          <t>-8,11; -1,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -3,83</t>
+          <t>-10,28; -3,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,97</t>
+          <t>-7,61; -2,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -3,03</t>
+          <t>-10,5; -4,81</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-28,16</t>
+          <t>-3,16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,49</t>
+          <t>-0,87</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,91</t>
+          <t>-7,37; -0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -1,93</t>
+          <t>-6,58; -0,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,94</t>
+          <t>-1,57; 4,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,7</t>
+          <t>-1,44; 4,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,98</t>
+          <t>-3,71; 0,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 0,33</t>
+          <t>-3,06; 1,49</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-30,31%</t>
+          <t>-3,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,73%</t>
+          <t>-0,94%</t>
         </is>
       </c>
     </row>
@@ -1175,22 +1175,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -0,99</t>
+          <t>-7,86; -0,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,64; -2,13</t>
+          <t>-6,99; -0,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,57</t>
+          <t>-1,67; 5,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 6,46</t>
+          <t>-1,51; 4,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 0,37</t>
+          <t>-3,29; 1,64</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,49</t>
+          <t>-5,16; 1,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,15</t>
+          <t>-6,23; 0,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,34</t>
+          <t>-3,88; 2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,62</t>
+          <t>-2,19; 2,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,26</t>
+          <t>-3,25; 1,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,8</t>
+          <t>-3,41; 0,72</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-2,42%</t>
+          <t>-3,09%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0,21%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,33%</t>
+          <t>-1,54%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,6</t>
+          <t>-5,36; 1,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 1,23</t>
+          <t>-6,48; 0,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,48</t>
+          <t>-4,04; 2,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,77</t>
+          <t>-2,28; 2,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,34</t>
+          <t>-3,39; 1,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,85</t>
+          <t>-3,54; 0,79</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,37</t>
+          <t>-2,42; 2,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,34</t>
+          <t>-3,34; 1,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,4</t>
+          <t>0,16; 5,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,77</t>
+          <t>-0,22; 4,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,03</t>
+          <t>-0,4; 2,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,19</t>
+          <t>-1,04; 2,35</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-1,07%</t>
+          <t>-1,23%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,46</t>
+          <t>-2,43; 2,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,39</t>
+          <t>-3,38; 1,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,87</t>
+          <t>0,17; 5,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,19</t>
+          <t>-0,2; 5,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,16</t>
+          <t>-0,41; 3,04</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,36</t>
+          <t>-1,07; 2,48</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-1,17</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,92</t>
+          <t>-1,73; 3,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,77</t>
+          <t>-1,08; 4,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,19</t>
+          <t>-2,52; 1,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; -0,41</t>
+          <t>-4,69; -0,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,69</t>
+          <t>-1,47; 1,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,48</t>
+          <t>-2,57; 0,41</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-2,42%</t>
+          <t>-2,72%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,0%</t>
+          <t>-1,19%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,16</t>
+          <t>-1,76; 3,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,98</t>
+          <t>-1,1; 4,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,21</t>
+          <t>-2,55; 1,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,42</t>
+          <t>-4,7; -0,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,74</t>
+          <t>-1,49; 1,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,49</t>
+          <t>-2,61; 0,42</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-7,66</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,03</t>
+          <t>-3,52; -0,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -1,13</t>
+          <t>-4,83; -0,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,65</t>
+          <t>-1,29; 1,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,1</t>
+          <t>-2,56; 0,49</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,36</t>
+          <t>-1,9; 0,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -0,77</t>
+          <t>-3,13; -0,66</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-8,97%</t>
+          <t>-3,08%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-2,14%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,03</t>
+          <t>-4,07; -0,02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -1,35</t>
+          <t>-5,64; -0,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,85</t>
+          <t>-1,42; 1,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,22</t>
+          <t>-2,83; 0,55</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,41</t>
+          <t>-2,15; 0,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -0,9</t>
+          <t>-3,56; -0,78</t>
         </is>
       </c>
     </row>
